--- a/data/Lookup_Tables/scv_referencia.XLSX
+++ b/data/Lookup_Tables/scv_referencia.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/mmcamacho_comillas_edu/Documents/Archivos de chat de Microsoft Teams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beatrizreglero/Desktop/TFG/TFG_Entregas/data/Lookup_Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBD4918A-AD5A-43DD-A6DE-D30867C67BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1F9589-BB8B-6541-87D9-1522561554EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{AC2CF289-66E2-448C-B1A4-DB09717E46AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="22700" windowHeight="14480" xr2:uid="{AC2CF289-66E2-448C-B1A4-DB09717E46AC}"/>
   </bookViews>
   <sheets>
     <sheet name="scv_referencia" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>zona referencia</t>
   </si>
@@ -60,33 +57,9 @@
     <t>A3</t>
   </si>
   <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>36,67</t>
-  </si>
-  <si>
-    <t>26,34</t>
-  </si>
-  <si>
-    <t>21,7</t>
-  </si>
-  <si>
-    <t>14,9</t>
-  </si>
-  <si>
     <t>A4</t>
   </si>
   <si>
-    <t>50,93</t>
-  </si>
-  <si>
-    <t>36,89</t>
-  </si>
-  <si>
-    <t>30,3</t>
-  </si>
-  <si>
     <t>B3</t>
   </si>
   <si>
@@ -96,25 +69,7 @@
     <t>C1</t>
   </si>
   <si>
-    <t>0,2146</t>
-  </si>
-  <si>
     <t>C2</t>
-  </si>
-  <si>
-    <t>0,7304</t>
-  </si>
-  <si>
-    <t>18,33</t>
-  </si>
-  <si>
-    <t>12,76</t>
-  </si>
-  <si>
-    <t>10,7</t>
-  </si>
-  <si>
-    <t>7,1</t>
   </si>
   <si>
     <t>C3</t>
@@ -151,10 +106,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -182,7 +144,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -201,9 +163,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +203,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -347,7 +309,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,7 +451,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -498,9 +460,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB0D97A-DCD1-4417-8A42-D8AFFC29DC06}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,324 +482,324 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="C3" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="D3" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="E3" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F3" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" s="1">
+        <v>1.6910000000000001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>50.93</v>
+      </c>
+      <c r="D4" s="1">
+        <v>36.89</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30.3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B5" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="D5" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="E5" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F5" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B6" s="1">
+        <v>1.6910000000000001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>50.93</v>
+      </c>
+      <c r="D6" s="1">
+        <v>36.89</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B7" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="B8" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="C8" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D8" s="1">
+        <v>12.76</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1">
-        <v>1691</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B9" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="C9" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="D9" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="E9" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F9" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B10" s="1">
+        <v>1.6910000000000001</v>
+      </c>
+      <c r="C10" s="1">
+        <v>50.93</v>
+      </c>
+      <c r="D10" s="1">
+        <v>36.89</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30.3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B11" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="F4">
+      <c r="B12" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12.76</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F12" s="1">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="D13" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="E13" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F13" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="C15" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="D15" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="E15" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F15" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="C16" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D16" s="1">
+        <v>12.76</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F16" s="1">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="C17" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D17" s="1">
+        <v>12.76</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F17" s="1">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1691</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1691</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
+      <c r="B18" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="C18" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D18" s="1">
+        <v>12.76</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -846,6 +808,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008CC35A7A26A4324F8F38BD84F25AF9C1" ma:contentTypeVersion="7" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b819923d2297222e9ee10f9e0fee1a03">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b193dfaa-deae-48b4-a85f-1fcd6ead3755" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db138671d8e145de4e330d26d84748c1" ns2:_="">
     <xsd:import namespace="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
@@ -1007,29 +984,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F3D661-0569-4E01-B41C-54FD677327CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59752139-11EF-47F1-917D-ACD62F85A532}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79CBC933-6423-46BE-AF75-94AE57DB9DB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79CBC933-6423-46BE-AF75-94AE57DB9DB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59752139-11EF-47F1-917D-ACD62F85A532}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F3D661-0569-4E01-B41C-54FD677327CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>